--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -1,37 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Universidad\2025-2\Asistencia\Laboratorios\Lab6\ISIS1225-Laboratorio-6\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Laboratorio6-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC64618-C61A-4319-8649-3E83499ED108}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Lab6" sheetId="1" r:id="rId1"/>
     <sheet name="Graf Mem Vs Tiempo" sheetId="17" r:id="rId2"/>
     <sheet name="Graf LF Vs Mem" sheetId="15" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -233,6 +225,58 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -329,58 +373,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -528,7 +520,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -615,7 +607,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -626,6 +618,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>687028.45800781203</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>420006.18457031198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>404024.26269531198</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>390973.60644531198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -635,6 +639,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>6967.0678000450098</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5240.1049998998596</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5595.3789999484998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5012.6747000217401</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -722,7 +738,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -835,7 +851,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -873,7 +889,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1087681551"/>
@@ -960,7 +976,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -998,7 +1014,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1087686127"/>
@@ -1040,7 +1056,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1070,7 +1086,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="es-CO"/>
     </a:p>
   </c:txPr>
 </c:chartSpace>
@@ -1143,7 +1159,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1267,7 +1283,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1299,6 +1315,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>687028.45800781203</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>420006.18457031198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>404024.26269531198</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>390973.60644531198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1413,7 +1441,7 @@
                       <a:cs typeface="+mn-cs"/>
                     </a:defRPr>
                   </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
+                  <a:endParaRPr lang="es-CO"/>
                 </a:p>
               </c:txPr>
             </c:trendlineLbl>
@@ -1533,7 +1561,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1568,7 +1596,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1086959919"/>
@@ -1641,7 +1669,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="es-CO"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1675,7 +1703,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1086958255"/>
@@ -1714,7 +1742,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="es-CO"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1744,7 +1772,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="es-CO"/>
     </a:p>
   </c:txPr>
 </c:chartSpace>
@@ -2906,29 +2934,29 @@
   <autoFilter ref="A2:C6" xr:uid="{B245DDE7-54F2-4A7A-AC17-5CA17DD7B03F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A7AF2A2F-BC4B-404E-9B8B-256DA178E68B}" name="Factor de Carga (PROBING)"/>
-    <tableColumn id="5" xr3:uid="{F280BCD9-1105-4F25-860B-4E27D28E75B2}" name="Consumo de Datos [kB]" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tiempo de Ejecución Real @LP [ms]" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{F280BCD9-1105-4F25-860B-4E27D28E75B2}" name="Consumo de Datos [kB]" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tiempo de Ejecución Real @LP [ms]" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A10:C14" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A10:C14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
   <autoFilter ref="A10:C14" xr:uid="{5C24B5A8-1B8E-4092-B34A-66FF5413D106}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Factor de Carga (CHAINING)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{89028F05-533D-401C-8D1A-1C8737D88894}" name="Consumo de Datos [kB]" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tiempo de Ejecución Real @SC [ms]" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Factor de Carga (CHAINING)" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{89028F05-533D-401C-8D1A-1C8737D88894}" name="Consumo de Datos [kB]" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tiempo de Ejecución Real @SC [ms]" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2966,7 +2994,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3072,7 +3100,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3214,7 +3242,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3223,21 +3251,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.7265625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.1796875" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
     </row>
-    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -3248,42 +3276,58 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>0.1</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="7"/>
+      <c r="B3" s="5">
+        <v>687028.45800781203</v>
+      </c>
+      <c r="C3" s="7">
+        <v>6967.0678000450098</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="9">
         <v>0.5</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7"/>
+      <c r="B4" s="2">
+        <v>420006.18457031198</v>
+      </c>
+      <c r="C4" s="7">
+        <v>5240.1049998998596</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>0.7</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
+      <c r="B5" s="2">
+        <v>404024.26269531198</v>
+      </c>
+      <c r="C5" s="7">
+        <v>5595.3789999484998</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="10">
         <v>0.9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="B6" s="2">
+        <v>390973.60644531198</v>
+      </c>
+      <c r="C6" s="7">
+        <v>5012.6747000217401</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="18.5" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="11"/>
       <c r="C9" s="11"/>
     </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -3294,35 +3338,35 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>2</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="5"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>4</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>6</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>8</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
@@ -3348,6 +3392,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010023858CF01A2EF24688B692775F4C60A4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="af74a0f8eb440a60883e9dd833f0742f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="164883f8-7691-4ecf-b54a-664c0d0edefe" xmlns:ns3="85e30bcc-d76c-4413-8e4d-2dce22fb0743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ceeff32ffca1089660572a8ebd1782" ns2:_="" ns3:_="">
     <xsd:import namespace="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
@@ -3596,15 +3649,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
@@ -3617,6 +3661,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10B9E65-6C88-4633-81F7-F02338B2B10B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3633,12 +3685,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f37e920cb68ed4a8/Desktop/Laboratorio6-G03/Docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FC64618-C61A-4319-8649-3E83499ED108}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9FD380-61A2-49FF-B83F-A65988C44B82}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
@@ -225,58 +225,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -373,6 +321,58 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -749,6 +749,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>405776.23144531198</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>397646.18457031198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>395338.306640625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>394248.58300781198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -758,6 +770,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4822.9373999833997</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4571.1498999595597</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6400.9654999971299</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5378.4332998991003</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1473,6 +1497,18 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>405776.23144531198</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>397646.18457031198</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>395338.306640625</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>394248.58300781198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2934,20 +2970,20 @@
   <autoFilter ref="A2:C6" xr:uid="{B245DDE7-54F2-4A7A-AC17-5CA17DD7B03F}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{A7AF2A2F-BC4B-404E-9B8B-256DA178E68B}" name="Factor de Carga (PROBING)"/>
-    <tableColumn id="5" xr3:uid="{F280BCD9-1105-4F25-860B-4E27D28E75B2}" name="Consumo de Datos [kB]" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tiempo de Ejecución Real @LP [ms]" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{F280BCD9-1105-4F25-860B-4E27D28E75B2}" name="Consumo de Datos [kB]" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tiempo de Ejecución Real @LP [ms]" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A10:C14" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A10:C14" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A10:C14" xr:uid="{5C24B5A8-1B8E-4092-B34A-66FF5413D106}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Factor de Carga (CHAINING)" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{89028F05-533D-401C-8D1A-1C8737D88894}" name="Consumo de Datos [kB]" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tiempo de Ejecución Real @SC [ms]" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Factor de Carga (CHAINING)" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{89028F05-533D-401C-8D1A-1C8737D88894}" name="Consumo de Datos [kB]" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tiempo de Ejecución Real @SC [ms]" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3342,29 +3378,45 @@
       <c r="A11" s="2">
         <v>2</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
+      <c r="B11" s="2">
+        <v>405776.23144531198</v>
+      </c>
+      <c r="C11" s="5">
+        <v>4822.9373999833997</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>4</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="B12" s="2">
+        <v>397646.18457031198</v>
+      </c>
+      <c r="C12" s="2">
+        <v>4571.1498999595597</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>6</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
+      <c r="B13" s="2">
+        <v>395338.306640625</v>
+      </c>
+      <c r="C13" s="2">
+        <v>6400.9654999971299</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
+      <c r="B14" s="2">
+        <v>394248.58300781198</v>
+      </c>
+      <c r="C14" s="2">
+        <v>5378.4332998991003</v>
+      </c>
     </row>
     <row r="23" ht="14.65" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
@@ -3392,15 +3444,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010023858CF01A2EF24688B692775F4C60A4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="af74a0f8eb440a60883e9dd833f0742f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="164883f8-7691-4ecf-b54a-664c0d0edefe" xmlns:ns3="85e30bcc-d76c-4413-8e4d-2dce22fb0743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ceeff32ffca1089660572a8ebd1782" ns2:_="" ns3:_="">
     <xsd:import namespace="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
@@ -3649,6 +3692,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
@@ -3661,14 +3713,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10B9E65-6C88-4633-81F7-F02338B2B10B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3685,4 +3729,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Docs/TablasDatos-Lab6.xlsx
+++ b/Docs/TablasDatos-Lab6.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{FD33DA02-4501-4B58-9D83-E0FFBD1B4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9FD380-61A2-49FF-B83F-A65988C44B82}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="1300" yWindow="3110" windowWidth="14400" windowHeight="8170" tabRatio="767" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Lab6" sheetId="1" r:id="rId1"/>
@@ -2903,7 +2903,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9293175" cy="6067778"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -2936,7 +2936,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9297051" cy="6073205"/>
+    <xdr:ext cx="9293175" cy="6067778"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -3444,6 +3444,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010023858CF01A2EF24688B692775F4C60A4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="af74a0f8eb440a60883e9dd833f0742f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="164883f8-7691-4ecf-b54a-664c0d0edefe" xmlns:ns3="85e30bcc-d76c-4413-8e4d-2dce22fb0743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ceeff32ffca1089660572a8ebd1782" ns2:_="" ns3:_="">
     <xsd:import namespace="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
@@ -3692,15 +3701,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
@@ -3713,6 +3713,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E10B9E65-6C88-4633-81F7-F02338B2B10B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3729,12 +3737,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>